--- a/Result/profitability/8176.xlsx
+++ b/Result/profitability/8176.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.105</v>
       </c>
       <c r="N2" t="n">
-        <v>32.88875</v>
+        <v>34.12</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.11125</v>
+        <v>0.05875</v>
       </c>
       <c r="N3" t="n">
-        <v>31.61625</v>
+        <v>32.67625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13625</v>
+        <v>0.1275</v>
       </c>
       <c r="N4" t="n">
-        <v>30.3425</v>
+        <v>31.78</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0.18</v>
+        <v>0.20375</v>
       </c>
       <c r="N5" t="n">
-        <v>31.66625</v>
+        <v>33.49</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23</v>
+        <v>0.2125</v>
       </c>
       <c r="N6" t="n">
-        <v>29.67875</v>
+        <v>30.36875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2425</v>
+        <v>0.24625</v>
       </c>
       <c r="N7" t="n">
-        <v>26.77375</v>
+        <v>26.995</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8937,6 +8937,133 @@
       </c>
       <c r="AM67" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8176</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>101</v>
+      </c>
+      <c r="D68" t="n">
+        <v>58</v>
+      </c>
+      <c r="E68" t="n">
+        <v>43</v>
+      </c>
+      <c r="F68" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="G68" t="n">
+        <v>9</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>9.38%</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>8</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="N68" t="n">
+        <v>35.53875</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X68" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.059999999999995</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.05124378109452721</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>-2.111111111111111</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.5272858691723887</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
